--- a/AgentIssue-Bench Spreadsheet.xlsx
+++ b/AgentIssue-Bench Spreadsheet.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3728" uniqueCount="1535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3729" uniqueCount="1536">
   <si>
     <t>No.</t>
   </si>
@@ -5120,6 +5120,9 @@
   </si>
   <si>
     <t>a flaw in the Vercel AI SDK's utility that converts Zod schemas into the OpenAPI v3 format. When the converter encountered an optional Zod type (e.g., z.string().optional().describe(...)), it correctly identified that the type could be string or null, but it failed to copy the description and other metadata from the original Zod schema into the final OpenAPI schema.</t>
+  </si>
+  <si>
+    <t>Function-level7</t>
   </si>
 </sst>
 </file>
@@ -5881,7 +5884,17 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="96">
+  <dxfs count="97">
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
@@ -6957,14 +6970,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E22" totalsRowShown="0" headerRowDxfId="95" dataDxfId="93" headerRowBorderDxfId="94" tableBorderDxfId="92" totalsRowBorderDxfId="91">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:E22" totalsRowShown="0" headerRowDxfId="96" dataDxfId="94" headerRowBorderDxfId="95" tableBorderDxfId="93" totalsRowBorderDxfId="92">
   <autoFilter ref="A1:E22"/>
   <tableColumns count="5">
-    <tableColumn id="1" name="Category" dataDxfId="90"/>
-    <tableColumn id="2" name="Sub-category" dataDxfId="89"/>
-    <tableColumn id="3" name="Description" dataDxfId="88"/>
-    <tableColumn id="4" name="Replicated Count" dataDxfId="87"/>
-    <tableColumn id="5" name="Total Count" dataDxfId="86"/>
+    <tableColumn id="1" name="Category" dataDxfId="91"/>
+    <tableColumn id="2" name="Sub-category" dataDxfId="90"/>
+    <tableColumn id="3" name="Description" dataDxfId="89"/>
+    <tableColumn id="4" name="Replicated Count" dataDxfId="88"/>
+    <tableColumn id="5" name="Total Count" dataDxfId="87"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6974,53 +6987,53 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Table3" displayName="Table3" ref="A3:C6" totalsRowShown="0">
   <autoFilter ref="A3:C6"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="SE Agents" dataDxfId="85"/>
-    <tableColumn id="2" name="gpt-4o" dataDxfId="84"/>
-    <tableColumn id="3" name="claude-3.5" dataDxfId="83"/>
+    <tableColumn id="1" name="SE Agents" dataDxfId="86"/>
+    <tableColumn id="2" name="gpt-4o" dataDxfId="85"/>
+    <tableColumn id="3" name="claude-3.5" dataDxfId="84"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A12:I32" totalsRowShown="0" headerRowDxfId="82" dataDxfId="81" tableBorderDxfId="80">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="Table7" displayName="Table7" ref="A12:I32" totalsRowShown="0" headerRowDxfId="83" dataDxfId="82" tableBorderDxfId="81">
   <autoFilter ref="A12:I32"/>
   <tableColumns count="9">
-    <tableColumn id="1" name="Category" dataDxfId="79"/>
-    <tableColumn id="2" name="Sub-category" dataDxfId="78"/>
-    <tableColumn id="3" name="Agentless" dataDxfId="77"/>
-    <tableColumn id="4" name="SWE-Agent" dataDxfId="76"/>
-    <tableColumn id="5" name="AutoCodeRover" dataDxfId="75"/>
-    <tableColumn id="6" name="Agentless2" dataDxfId="74"/>
-    <tableColumn id="7" name="SWE-Agent3" dataDxfId="73"/>
-    <tableColumn id="8" name="AutoCodeRover4" dataDxfId="72"/>
-    <tableColumn id="9" name="Total" dataDxfId="71"/>
+    <tableColumn id="1" name="Category" dataDxfId="80"/>
+    <tableColumn id="2" name="Sub-category" dataDxfId="79"/>
+    <tableColumn id="3" name="Agentless" dataDxfId="78"/>
+    <tableColumn id="4" name="SWE-Agent" dataDxfId="77"/>
+    <tableColumn id="5" name="AutoCodeRover" dataDxfId="76"/>
+    <tableColumn id="6" name="Agentless2" dataDxfId="75"/>
+    <tableColumn id="7" name="SWE-Agent3" dataDxfId="74"/>
+    <tableColumn id="8" name="AutoCodeRover4" dataDxfId="73"/>
+    <tableColumn id="9" name="Total" dataDxfId="72"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A53:G55" totalsRowShown="0" headerRowDxfId="70" dataDxfId="69" dataCellStyle="Percent">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="Table8" displayName="Table8" ref="A53:G55" totalsRowShown="0" headerRowDxfId="71" dataDxfId="70" dataCellStyle="Percent">
   <autoFilter ref="A53:G55"/>
   <tableColumns count="7">
-    <tableColumn id="1" name="Pass@k" dataDxfId="68" dataCellStyle="Hyperlink"/>
-    <tableColumn id="2" name="Agentless" dataDxfId="67" dataCellStyle="Percent">
+    <tableColumn id="1" name="Pass@k" dataDxfId="69" dataCellStyle="Hyperlink"/>
+    <tableColumn id="2" name="Agentless" dataDxfId="68" dataCellStyle="Percent">
       <calculatedColumnFormula>COUNTIF([1]!Table2[Correct], "&gt;0")/50</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" name="SWE-Agent" dataDxfId="66" dataCellStyle="Percent">
+    <tableColumn id="3" name="SWE-Agent" dataDxfId="67" dataCellStyle="Percent">
       <calculatedColumnFormula>COUNTIF([1]!Table2[Correct3],"&gt;0")/50</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" name="AutoCodeRover" dataDxfId="65" dataCellStyle="Percent">
+    <tableColumn id="4" name="AutoCodeRover" dataDxfId="66" dataCellStyle="Percent">
       <calculatedColumnFormula>COUNTIF([1]!Table2[Correct5],"&gt;0")/50</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" name="Agentless2" dataDxfId="64" dataCellStyle="Percent">
+    <tableColumn id="5" name="Agentless2" dataDxfId="65" dataCellStyle="Percent">
       <calculatedColumnFormula>COUNTIF([1]!Table2[Correct2],"&gt;0")/50</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" name="SWE-Agent3" dataDxfId="63" dataCellStyle="Percent">
+    <tableColumn id="6" name="SWE-Agent3" dataDxfId="64" dataCellStyle="Percent">
       <calculatedColumnFormula>COUNTIF([1]!Table2[Correct4],"&gt;0")/50</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="7" name="AutoCodeRover4" dataDxfId="62" dataCellStyle="Percent">
+    <tableColumn id="7" name="AutoCodeRover4" dataDxfId="63" dataCellStyle="Percent">
       <calculatedColumnFormula>COUNTIF([1]!Table2[Correct6],"&gt;0")/50</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -7029,43 +7042,44 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:AE52" totalsRowShown="0" headerRowDxfId="61" dataDxfId="60">
-  <autoFilter ref="A2:AE52"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A2:AF52" totalsRowShown="0" headerRowDxfId="62" dataDxfId="61">
+  <autoFilter ref="A2:AF52"/>
   <sortState ref="A3:AE52">
     <sortCondition ref="B2:B52"/>
   </sortState>
-  <tableColumns count="31">
-    <tableColumn id="1" name="No." dataDxfId="59"/>
-    <tableColumn id="31" name="Agent" dataDxfId="58"/>
-    <tableColumn id="2" name="Issue" dataDxfId="57"/>
-    <tableColumn id="3" name="Taxonomy" dataDxfId="56"/>
-    <tableColumn id="4" name="Sub-Category" dataDxfId="55"/>
-    <tableColumn id="5" name="Status" dataDxfId="54"/>
-    <tableColumn id="6" name="Reference" dataDxfId="53"/>
-    <tableColumn id="7" name="Plausible" dataDxfId="52"/>
-    <tableColumn id="8" name="Correct" dataDxfId="51"/>
-    <tableColumn id="9" name="File-level" dataDxfId="50"/>
-    <tableColumn id="10" name="Function-level" dataDxfId="49"/>
-    <tableColumn id="11" name="Plausible2" dataDxfId="48"/>
-    <tableColumn id="12" name="Correct2" dataDxfId="47"/>
-    <tableColumn id="13" name="File-level2" dataDxfId="46"/>
-    <tableColumn id="14" name="Function-level2" dataDxfId="45"/>
-    <tableColumn id="15" name="Plausible3" dataDxfId="44"/>
-    <tableColumn id="16" name="Correct3" dataDxfId="43"/>
-    <tableColumn id="17" name="File-level3" dataDxfId="42"/>
-    <tableColumn id="18" name="Function-level3" dataDxfId="41"/>
-    <tableColumn id="19" name="Plausible4" dataDxfId="40"/>
-    <tableColumn id="20" name="Correct4" dataDxfId="39"/>
-    <tableColumn id="21" name="File-level4" dataDxfId="38"/>
-    <tableColumn id="22" name="Function-level4" dataDxfId="37"/>
-    <tableColumn id="23" name="Plausible5" dataDxfId="36"/>
-    <tableColumn id="24" name="Correct5" dataDxfId="35"/>
-    <tableColumn id="25" name="File-level5" dataDxfId="34"/>
-    <tableColumn id="26" name="Function-level5" dataDxfId="33"/>
-    <tableColumn id="27" name="Plausible6" dataDxfId="32"/>
-    <tableColumn id="28" name="Correct6" dataDxfId="31"/>
-    <tableColumn id="29" name="File-level6" dataDxfId="30"/>
-    <tableColumn id="30" name="Function-level6" dataDxfId="29"/>
+  <tableColumns count="32">
+    <tableColumn id="1" name="No." dataDxfId="60"/>
+    <tableColumn id="31" name="Agent" dataDxfId="59"/>
+    <tableColumn id="2" name="Issue" dataDxfId="58"/>
+    <tableColumn id="3" name="Taxonomy" dataDxfId="57"/>
+    <tableColumn id="4" name="Sub-Category" dataDxfId="56"/>
+    <tableColumn id="5" name="Status" dataDxfId="55"/>
+    <tableColumn id="6" name="Reference" dataDxfId="54"/>
+    <tableColumn id="7" name="Plausible" dataDxfId="53"/>
+    <tableColumn id="8" name="Correct" dataDxfId="52"/>
+    <tableColumn id="9" name="File-level" dataDxfId="51"/>
+    <tableColumn id="10" name="Function-level" dataDxfId="50"/>
+    <tableColumn id="11" name="Plausible2" dataDxfId="49"/>
+    <tableColumn id="12" name="Correct2" dataDxfId="48"/>
+    <tableColumn id="13" name="File-level2" dataDxfId="47"/>
+    <tableColumn id="14" name="Function-level2" dataDxfId="46"/>
+    <tableColumn id="15" name="Plausible3" dataDxfId="45"/>
+    <tableColumn id="16" name="Correct3" dataDxfId="44"/>
+    <tableColumn id="17" name="File-level3" dataDxfId="43"/>
+    <tableColumn id="18" name="Function-level3" dataDxfId="42"/>
+    <tableColumn id="19" name="Plausible4" dataDxfId="41"/>
+    <tableColumn id="20" name="Correct4" dataDxfId="40"/>
+    <tableColumn id="21" name="File-level4" dataDxfId="39"/>
+    <tableColumn id="22" name="Function-level4" dataDxfId="38"/>
+    <tableColumn id="23" name="Plausible5" dataDxfId="37"/>
+    <tableColumn id="24" name="Correct5" dataDxfId="36"/>
+    <tableColumn id="25" name="File-level5" dataDxfId="35"/>
+    <tableColumn id="26" name="Function-level5" dataDxfId="34"/>
+    <tableColumn id="27" name="Plausible6" dataDxfId="33"/>
+    <tableColumn id="28" name="Correct6" dataDxfId="32"/>
+    <tableColumn id="29" name="File-level6" dataDxfId="31"/>
+    <tableColumn id="30" name="Function-level6" dataDxfId="30"/>
+    <tableColumn id="32" name="Function-level7" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7076,35 +7090,35 @@
   <autoFilter ref="A2:AD22"/>
   <tableColumns count="30">
     <tableColumn id="1" name="No."/>
-    <tableColumn id="2" name="Agent" dataDxfId="28"/>
-    <tableColumn id="3" name="Issue" dataDxfId="27"/>
-    <tableColumn id="4" name="Taxonomy" dataDxfId="26"/>
-    <tableColumn id="5" name="Sub-Category" dataDxfId="25"/>
-    <tableColumn id="6" name="Reference" dataDxfId="24"/>
-    <tableColumn id="7" name="Plausible" dataDxfId="23"/>
-    <tableColumn id="8" name="Correct" dataDxfId="22"/>
-    <tableColumn id="9" name="File-level" dataDxfId="21"/>
-    <tableColumn id="10" name="Function-level" dataDxfId="20"/>
-    <tableColumn id="11" name="Plausible2" dataDxfId="19"/>
-    <tableColumn id="12" name="Correct2" dataDxfId="18"/>
-    <tableColumn id="13" name="File-level2" dataDxfId="17"/>
-    <tableColumn id="14" name="Function-level2" dataDxfId="16"/>
-    <tableColumn id="15" name="Plausible3" dataDxfId="15"/>
-    <tableColumn id="16" name="Correct3" dataDxfId="14"/>
-    <tableColumn id="17" name="File-level3" dataDxfId="13"/>
-    <tableColumn id="18" name="Function-level3" dataDxfId="12"/>
-    <tableColumn id="19" name="Plausible4" dataDxfId="11"/>
-    <tableColumn id="20" name="Correct4" dataDxfId="10"/>
-    <tableColumn id="21" name="File-level4" dataDxfId="9"/>
-    <tableColumn id="22" name="Function-level4" dataDxfId="8"/>
-    <tableColumn id="23" name="Plausible5" dataDxfId="7"/>
-    <tableColumn id="24" name="Correct5" dataDxfId="6"/>
-    <tableColumn id="25" name="File-level5" dataDxfId="5"/>
-    <tableColumn id="26" name="Function-level5" dataDxfId="4"/>
-    <tableColumn id="27" name="Plausible6" dataDxfId="3"/>
-    <tableColumn id="28" name="Correct6" dataDxfId="2"/>
-    <tableColumn id="29" name="File-level6" dataDxfId="1"/>
-    <tableColumn id="30" name="Function-level6" dataDxfId="0"/>
+    <tableColumn id="2" name="Agent" dataDxfId="29"/>
+    <tableColumn id="3" name="Issue" dataDxfId="28"/>
+    <tableColumn id="4" name="Taxonomy" dataDxfId="27"/>
+    <tableColumn id="5" name="Sub-Category" dataDxfId="26"/>
+    <tableColumn id="6" name="Reference" dataDxfId="25"/>
+    <tableColumn id="7" name="Plausible" dataDxfId="24"/>
+    <tableColumn id="8" name="Correct" dataDxfId="23"/>
+    <tableColumn id="9" name="File-level" dataDxfId="22"/>
+    <tableColumn id="10" name="Function-level" dataDxfId="21"/>
+    <tableColumn id="11" name="Plausible2" dataDxfId="20"/>
+    <tableColumn id="12" name="Correct2" dataDxfId="19"/>
+    <tableColumn id="13" name="File-level2" dataDxfId="18"/>
+    <tableColumn id="14" name="Function-level2" dataDxfId="17"/>
+    <tableColumn id="15" name="Plausible3" dataDxfId="16"/>
+    <tableColumn id="16" name="Correct3" dataDxfId="15"/>
+    <tableColumn id="17" name="File-level3" dataDxfId="14"/>
+    <tableColumn id="18" name="Function-level3" dataDxfId="13"/>
+    <tableColumn id="19" name="Plausible4" dataDxfId="12"/>
+    <tableColumn id="20" name="Correct4" dataDxfId="11"/>
+    <tableColumn id="21" name="File-level4" dataDxfId="10"/>
+    <tableColumn id="22" name="Function-level4" dataDxfId="9"/>
+    <tableColumn id="23" name="Plausible5" dataDxfId="8"/>
+    <tableColumn id="24" name="Correct5" dataDxfId="7"/>
+    <tableColumn id="25" name="File-level5" dataDxfId="6"/>
+    <tableColumn id="26" name="Function-level5" dataDxfId="5"/>
+    <tableColumn id="27" name="Plausible6" dataDxfId="4"/>
+    <tableColumn id="28" name="Correct6" dataDxfId="3"/>
+    <tableColumn id="29" name="File-level6" dataDxfId="2"/>
+    <tableColumn id="30" name="Function-level6" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -8821,7 +8835,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE55"/>
+  <dimension ref="A1:AF55"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="12.47265625" customWidth="1"/>
@@ -8830,7 +8844,7 @@
     <col min="7" max="7" width="11.26171875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="H1" s="135" t="s">
         <v>51</v>
       </c>
@@ -8868,7 +8882,7 @@
       <c r="AD1" s="135"/>
       <c r="AE1" s="135"/>
     </row>
-    <row r="2" spans="1:31" ht="28.8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:32" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -8962,8 +8976,11 @@
       <c r="AE2" s="1" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="3" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF2" s="1" t="s">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="22">
         <v>1</v>
       </c>
@@ -9057,8 +9074,9 @@
       <c r="AE3" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF3" s="3"/>
+    </row>
+    <row r="4" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="22">
         <v>2</v>
       </c>
@@ -9158,8 +9176,9 @@
         <f>(2/3)/3</f>
         <v>0.22222222222222221</v>
       </c>
-    </row>
-    <row r="5" spans="1:31" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF4" s="3"/>
+    </row>
+    <row r="5" spans="1:32" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="22">
         <v>3</v>
       </c>
@@ -9252,8 +9271,9 @@
       <c r="AE5" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF5" s="3"/>
+    </row>
+    <row r="6" spans="1:32" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="22">
         <v>4</v>
       </c>
@@ -9349,8 +9369,9 @@
       <c r="AE6" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:31" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF6" s="3"/>
+    </row>
+    <row r="7" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="22">
         <v>5</v>
       </c>
@@ -9446,8 +9467,9 @@
         <f>(2/11)/3</f>
         <v>6.0606060606060608E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF7" s="3"/>
+    </row>
+    <row r="8" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="22">
         <v>6</v>
       </c>
@@ -9543,8 +9565,9 @@
         <f>(1/4)/3</f>
         <v>8.3333333333333329E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" ht="144" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF8" s="3"/>
+    </row>
+    <row r="9" spans="1:32" ht="144" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="22">
         <v>7</v>
       </c>
@@ -9637,26 +9660,27 @@
       <c r="AE9" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF9" s="3"/>
+    </row>
+    <row r="10" spans="1:32" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="22">
         <v>8</v>
       </c>
-      <c r="B10" s="22" t="s">
-        <v>149</v>
+      <c r="B10" s="34" t="s">
+        <v>262</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>152</v>
+        <v>271</v>
       </c>
       <c r="D10" s="22" t="s">
         <v>151</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>151</v>
+        <v>241</v>
       </c>
       <c r="F10" s="22"/>
-      <c r="G10" s="23" t="s">
-        <v>8</v>
+      <c r="G10" s="22" t="s">
+        <v>272</v>
       </c>
       <c r="H10" s="6">
         <v>0</v>
@@ -9670,7 +9694,7 @@
       <c r="K10" s="4">
         <v>0</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="3">
         <v>0</v>
       </c>
       <c r="M10" s="3">
@@ -9682,7 +9706,7 @@
       <c r="O10" s="4">
         <v>0</v>
       </c>
-      <c r="P10" s="5">
+      <c r="P10" s="3">
         <v>0</v>
       </c>
       <c r="Q10" s="3">
@@ -9694,7 +9718,7 @@
       <c r="S10" s="4">
         <v>0</v>
       </c>
-      <c r="T10" s="5">
+      <c r="T10" s="3">
         <v>0</v>
       </c>
       <c r="U10" s="3">
@@ -9706,7 +9730,7 @@
       <c r="W10" s="4">
         <v>0</v>
       </c>
-      <c r="X10" s="5">
+      <c r="X10" s="3">
         <v>0</v>
       </c>
       <c r="Y10" s="3">
@@ -9718,7 +9742,7 @@
       <c r="AA10" s="4">
         <v>0</v>
       </c>
-      <c r="AB10" s="5">
+      <c r="AB10" s="3">
         <v>0</v>
       </c>
       <c r="AC10" s="3">
@@ -9727,11 +9751,14 @@
       <c r="AD10" s="3">
         <v>0</v>
       </c>
-      <c r="AE10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AE10" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="22">
         <v>9</v>
       </c>
@@ -9823,8 +9850,9 @@
       <c r="AE11" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="22">
         <v>10</v>
       </c>
@@ -9918,8 +9946,9 @@
       <c r="AE12" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF12" s="3"/>
+    </row>
+    <row r="13" spans="1:32" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="22">
         <v>11</v>
       </c>
@@ -10012,8 +10041,9 @@
       <c r="AE13" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF13" s="3"/>
+    </row>
+    <row r="14" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="22">
         <v>12</v>
       </c>
@@ -10107,8 +10137,9 @@
       <c r="AE14" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF14" s="3"/>
+    </row>
+    <row r="15" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="22">
         <v>13</v>
       </c>
@@ -10200,8 +10231,9 @@
       <c r="AE15" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF15" s="3"/>
+    </row>
+    <row r="16" spans="1:32" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="22">
         <v>14</v>
       </c>
@@ -10294,8 +10326,9 @@
       <c r="AE16" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="1:32" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="22">
         <v>15</v>
       </c>
@@ -10395,8 +10428,9 @@
         <f>(1/7)/3</f>
         <v>4.7619047619047616E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF17" s="3"/>
+    </row>
+    <row r="18" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="22">
         <v>16</v>
       </c>
@@ -10489,8 +10523,9 @@
         <f>1/2</f>
         <v>0.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" ht="187.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF18" s="3"/>
+    </row>
+    <row r="19" spans="1:32" ht="187.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="22">
         <v>17</v>
       </c>
@@ -10585,8 +10620,9 @@
       <c r="AE19" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" ht="115.2" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="1:32" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="22">
         <v>18</v>
       </c>
@@ -10684,8 +10720,9 @@
       <c r="AE20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF20" s="3"/>
+    </row>
+    <row r="21" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="22">
         <v>19</v>
       </c>
@@ -10784,8 +10821,9 @@
         <f>(3/17)/3</f>
         <v>5.8823529411764712E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF21" s="3"/>
+    </row>
+    <row r="22" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="22">
         <v>20</v>
       </c>
@@ -10888,8 +10926,9 @@
         <f>1/3</f>
         <v>0.33333333333333331</v>
       </c>
-    </row>
-    <row r="23" spans="1:31" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF22" s="3"/>
+    </row>
+    <row r="23" spans="1:32" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="22">
         <v>21</v>
       </c>
@@ -10983,8 +11022,9 @@
         <f>(1/3)/3</f>
         <v>0.1111111111111111</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF23" s="3"/>
+    </row>
+    <row r="24" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="22">
         <v>22</v>
       </c>
@@ -11076,8 +11116,9 @@
       <c r="AE24" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF24" s="3"/>
+    </row>
+    <row r="25" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="22">
         <v>23</v>
       </c>
@@ -11172,8 +11213,9 @@
         <f>(1/3)/3</f>
         <v>0.1111111111111111</v>
       </c>
-    </row>
-    <row r="26" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF25" s="3"/>
+    </row>
+    <row r="26" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="22">
         <v>24</v>
       </c>
@@ -11267,8 +11309,9 @@
       <c r="AE26" s="26">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:31" ht="129.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF26" s="3"/>
+    </row>
+    <row r="27" spans="1:32" ht="129.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="22">
         <v>25</v>
       </c>
@@ -11363,8 +11406,9 @@
         <f>(3/6)/3</f>
         <v>0.16666666666666666</v>
       </c>
-    </row>
-    <row r="28" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF27" s="3"/>
+    </row>
+    <row r="28" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="22">
         <v>26</v>
       </c>
@@ -11461,8 +11505,9 @@
         <f>1/7</f>
         <v>0.14285714285714285</v>
       </c>
-    </row>
-    <row r="29" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF28" s="3"/>
+    </row>
+    <row r="29" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="22">
         <v>27</v>
       </c>
@@ -11559,8 +11604,9 @@
       <c r="AE29" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF29" s="3"/>
+    </row>
+    <row r="30" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="22">
         <v>28</v>
       </c>
@@ -11654,8 +11700,9 @@
       <c r="AE30" s="3">
         <v>0.67</v>
       </c>
-    </row>
-    <row r="31" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF30" s="3"/>
+    </row>
+    <row r="31" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="22">
         <v>29</v>
       </c>
@@ -11749,8 +11796,9 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF31" s="3"/>
+    </row>
+    <row r="32" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="22">
         <v>30</v>
       </c>
@@ -11842,8 +11890,9 @@
       <c r="AE32" s="3">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF32" s="3"/>
+    </row>
+    <row r="33" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="22">
         <v>31</v>
       </c>
@@ -11935,8 +11984,9 @@
       <c r="AE33" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF33" s="3"/>
+    </row>
+    <row r="34" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="22">
         <v>32</v>
       </c>
@@ -12033,8 +12083,9 @@
         <f>(5/4)/3</f>
         <v>0.41666666666666669</v>
       </c>
-    </row>
-    <row r="35" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF34" s="3"/>
+    </row>
+    <row r="35" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="22">
         <v>33</v>
       </c>
@@ -12126,8 +12177,9 @@
       <c r="AE35" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF35" s="3"/>
+    </row>
+    <row r="36" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="22">
         <v>34</v>
       </c>
@@ -12221,8 +12273,9 @@
       <c r="AE36" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:31" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF36" s="3"/>
+    </row>
+    <row r="37" spans="1:32" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="22">
         <v>35</v>
       </c>
@@ -12316,8 +12369,9 @@
       <c r="AE37" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF37" s="3"/>
+    </row>
+    <row r="38" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="22">
         <v>36</v>
       </c>
@@ -12411,8 +12465,9 @@
       <c r="AE38" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF38" s="3"/>
+    </row>
+    <row r="39" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="22">
         <v>37</v>
       </c>
@@ -12505,8 +12560,9 @@
       <c r="AE39" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="40" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="22">
         <v>38</v>
       </c>
@@ -12599,8 +12655,9 @@
         <f>2/3</f>
         <v>0.66666666666666663</v>
       </c>
-    </row>
-    <row r="41" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="22">
         <v>39</v>
       </c>
@@ -12699,8 +12756,9 @@
       <c r="AE41" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF41" s="3"/>
+    </row>
+    <row r="42" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="22">
         <v>40</v>
       </c>
@@ -12792,8 +12850,9 @@
       <c r="AE42" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:31" ht="100.8" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF42" s="3"/>
+    </row>
+    <row r="43" spans="1:32" ht="100.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="22">
         <v>41</v>
       </c>
@@ -12885,8 +12944,9 @@
       <c r="AE43" s="4">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:31" ht="57.6" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF43" s="3"/>
+    </row>
+    <row r="44" spans="1:32" ht="57.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="22">
         <v>42</v>
       </c>
@@ -12981,8 +13041,9 @@
       <c r="AE44" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF44" s="3"/>
+    </row>
+    <row r="45" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="22">
         <v>43</v>
       </c>
@@ -13079,8 +13140,9 @@
       <c r="AE45" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="1:31" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF45" s="3"/>
+    </row>
+    <row r="46" spans="1:32" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="22">
         <v>44</v>
       </c>
@@ -13172,8 +13234,9 @@
       <c r="AE46" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF46" s="3"/>
+    </row>
+    <row r="47" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="22">
         <v>45</v>
       </c>
@@ -13269,8 +13332,9 @@
       <c r="AE47" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF47" s="3"/>
+    </row>
+    <row r="48" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="22">
         <v>46</v>
       </c>
@@ -13364,8 +13428,9 @@
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF48" s="3"/>
+    </row>
+    <row r="49" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="22">
         <v>47</v>
       </c>
@@ -13457,8 +13522,9 @@
       <c r="AE49" s="5">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF49" s="3"/>
+    </row>
+    <row r="50" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="22">
         <v>48</v>
       </c>
@@ -13552,8 +13618,9 @@
       <c r="AE50" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF50" s="3"/>
+    </row>
+    <row r="51" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="22">
         <v>49</v>
       </c>
@@ -13645,8 +13712,9 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="1:31" ht="72" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF51" s="3"/>
+    </row>
+    <row r="52" spans="1:32" ht="72" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="22">
         <v>50</v>
       </c>
@@ -13738,8 +13806,9 @@
       <c r="AE52" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+      <c r="AF52" s="3"/>
+    </row>
+    <row r="53" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="H53" s="20"/>
       <c r="K53" s="21"/>
       <c r="O53" s="21"/>
@@ -13747,7 +13816,7 @@
       <c r="W53" s="21"/>
       <c r="AA53" s="21"/>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="54" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="G54" s="7" t="s">
         <v>130</v>
       </c>
@@ -13848,7 +13917,7 @@
         <v>9.591016891605129</v>
       </c>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.55000000000000004">
+    <row r="55" spans="1:32" x14ac:dyDescent="0.55000000000000004">
       <c r="G55" s="7" t="s">
         <v>223</v>
       </c>
@@ -13999,20 +14068,19 @@
     <hyperlink ref="G20" r:id="rId38"/>
     <hyperlink ref="G22" r:id="rId39"/>
     <hyperlink ref="G9" r:id="rId40"/>
-    <hyperlink ref="G10" r:id="rId41"/>
-    <hyperlink ref="G11" r:id="rId42"/>
-    <hyperlink ref="G12" r:id="rId43"/>
-    <hyperlink ref="G13" r:id="rId44"/>
-    <hyperlink ref="G14" r:id="rId45"/>
-    <hyperlink ref="G15" r:id="rId46"/>
-    <hyperlink ref="G16" r:id="rId47"/>
-    <hyperlink ref="G17" r:id="rId48"/>
-    <hyperlink ref="G18" r:id="rId49"/>
-    <hyperlink ref="G50" r:id="rId50"/>
+    <hyperlink ref="G11" r:id="rId41"/>
+    <hyperlink ref="G12" r:id="rId42"/>
+    <hyperlink ref="G13" r:id="rId43"/>
+    <hyperlink ref="G14" r:id="rId44"/>
+    <hyperlink ref="G15" r:id="rId45"/>
+    <hyperlink ref="G16" r:id="rId46"/>
+    <hyperlink ref="G17" r:id="rId47"/>
+    <hyperlink ref="G18" r:id="rId48"/>
+    <hyperlink ref="G50" r:id="rId49"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId51"/>
+    <tablePart r:id="rId50"/>
   </tableParts>
 </worksheet>
 </file>
@@ -36550,12 +36618,18 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="P123:T123"/>
-    <mergeCell ref="V123:Y123"/>
-    <mergeCell ref="P184:T184"/>
-    <mergeCell ref="V184:Y184"/>
-    <mergeCell ref="S231:W231"/>
-    <mergeCell ref="Y231:AB231"/>
+    <mergeCell ref="AR84:AV84"/>
+    <mergeCell ref="S47:W47"/>
+    <mergeCell ref="X47:AB47"/>
+    <mergeCell ref="AC47:AG47"/>
+    <mergeCell ref="AH47:AL47"/>
+    <mergeCell ref="AM47:AQ47"/>
+    <mergeCell ref="AR47:AV47"/>
+    <mergeCell ref="S84:W84"/>
+    <mergeCell ref="X84:AB84"/>
+    <mergeCell ref="AC84:AG84"/>
+    <mergeCell ref="AH84:AL84"/>
+    <mergeCell ref="AM84:AQ84"/>
     <mergeCell ref="AR114:AV114"/>
     <mergeCell ref="S111:W111"/>
     <mergeCell ref="X111:AB111"/>
@@ -36568,18 +36642,12 @@
     <mergeCell ref="AC114:AG114"/>
     <mergeCell ref="AH114:AL114"/>
     <mergeCell ref="AM114:AQ114"/>
-    <mergeCell ref="AR84:AV84"/>
-    <mergeCell ref="S47:W47"/>
-    <mergeCell ref="X47:AB47"/>
-    <mergeCell ref="AC47:AG47"/>
-    <mergeCell ref="AH47:AL47"/>
-    <mergeCell ref="AM47:AQ47"/>
-    <mergeCell ref="AR47:AV47"/>
-    <mergeCell ref="S84:W84"/>
-    <mergeCell ref="X84:AB84"/>
-    <mergeCell ref="AC84:AG84"/>
-    <mergeCell ref="AH84:AL84"/>
-    <mergeCell ref="AM84:AQ84"/>
+    <mergeCell ref="P123:T123"/>
+    <mergeCell ref="V123:Y123"/>
+    <mergeCell ref="P184:T184"/>
+    <mergeCell ref="V184:Y184"/>
+    <mergeCell ref="S231:W231"/>
+    <mergeCell ref="Y231:AB231"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1"/>

--- a/AgentIssue-Bench Spreadsheet.xlsx
+++ b/AgentIssue-Bench Spreadsheet.xlsx
@@ -5887,16 +5887,6 @@
   <dxfs count="97">
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="2" formatCode="0.00"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="2" formatCode="0.00"/>
@@ -5980,6 +5970,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -7079,7 +7079,7 @@
     <tableColumn id="28" name="Correct6" dataDxfId="32"/>
     <tableColumn id="29" name="File-level6" dataDxfId="31"/>
     <tableColumn id="30" name="Function-level6" dataDxfId="30"/>
-    <tableColumn id="32" name="Function-level7" dataDxfId="0"/>
+    <tableColumn id="32" name="Function-level7" dataDxfId="29"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7090,35 +7090,35 @@
   <autoFilter ref="A2:AD22"/>
   <tableColumns count="30">
     <tableColumn id="1" name="No."/>
-    <tableColumn id="2" name="Agent" dataDxfId="29"/>
-    <tableColumn id="3" name="Issue" dataDxfId="28"/>
-    <tableColumn id="4" name="Taxonomy" dataDxfId="27"/>
-    <tableColumn id="5" name="Sub-Category" dataDxfId="26"/>
-    <tableColumn id="6" name="Reference" dataDxfId="25"/>
-    <tableColumn id="7" name="Plausible" dataDxfId="24"/>
-    <tableColumn id="8" name="Correct" dataDxfId="23"/>
-    <tableColumn id="9" name="File-level" dataDxfId="22"/>
-    <tableColumn id="10" name="Function-level" dataDxfId="21"/>
-    <tableColumn id="11" name="Plausible2" dataDxfId="20"/>
-    <tableColumn id="12" name="Correct2" dataDxfId="19"/>
-    <tableColumn id="13" name="File-level2" dataDxfId="18"/>
-    <tableColumn id="14" name="Function-level2" dataDxfId="17"/>
-    <tableColumn id="15" name="Plausible3" dataDxfId="16"/>
-    <tableColumn id="16" name="Correct3" dataDxfId="15"/>
-    <tableColumn id="17" name="File-level3" dataDxfId="14"/>
-    <tableColumn id="18" name="Function-level3" dataDxfId="13"/>
-    <tableColumn id="19" name="Plausible4" dataDxfId="12"/>
-    <tableColumn id="20" name="Correct4" dataDxfId="11"/>
-    <tableColumn id="21" name="File-level4" dataDxfId="10"/>
-    <tableColumn id="22" name="Function-level4" dataDxfId="9"/>
-    <tableColumn id="23" name="Plausible5" dataDxfId="8"/>
-    <tableColumn id="24" name="Correct5" dataDxfId="7"/>
-    <tableColumn id="25" name="File-level5" dataDxfId="6"/>
-    <tableColumn id="26" name="Function-level5" dataDxfId="5"/>
-    <tableColumn id="27" name="Plausible6" dataDxfId="4"/>
-    <tableColumn id="28" name="Correct6" dataDxfId="3"/>
-    <tableColumn id="29" name="File-level6" dataDxfId="2"/>
-    <tableColumn id="30" name="Function-level6" dataDxfId="1"/>
+    <tableColumn id="2" name="Agent" dataDxfId="28"/>
+    <tableColumn id="3" name="Issue" dataDxfId="27"/>
+    <tableColumn id="4" name="Taxonomy" dataDxfId="26"/>
+    <tableColumn id="5" name="Sub-Category" dataDxfId="25"/>
+    <tableColumn id="6" name="Reference" dataDxfId="24"/>
+    <tableColumn id="7" name="Plausible" dataDxfId="23"/>
+    <tableColumn id="8" name="Correct" dataDxfId="22"/>
+    <tableColumn id="9" name="File-level" dataDxfId="21"/>
+    <tableColumn id="10" name="Function-level" dataDxfId="20"/>
+    <tableColumn id="11" name="Plausible2" dataDxfId="19"/>
+    <tableColumn id="12" name="Correct2" dataDxfId="18"/>
+    <tableColumn id="13" name="File-level2" dataDxfId="17"/>
+    <tableColumn id="14" name="Function-level2" dataDxfId="16"/>
+    <tableColumn id="15" name="Plausible3" dataDxfId="15"/>
+    <tableColumn id="16" name="Correct3" dataDxfId="14"/>
+    <tableColumn id="17" name="File-level3" dataDxfId="13"/>
+    <tableColumn id="18" name="Function-level3" dataDxfId="12"/>
+    <tableColumn id="19" name="Plausible4" dataDxfId="11"/>
+    <tableColumn id="20" name="Correct4" dataDxfId="10"/>
+    <tableColumn id="21" name="File-level4" dataDxfId="9"/>
+    <tableColumn id="22" name="Function-level4" dataDxfId="8"/>
+    <tableColumn id="23" name="Plausible5" dataDxfId="7"/>
+    <tableColumn id="24" name="Correct5" dataDxfId="6"/>
+    <tableColumn id="25" name="File-level5" dataDxfId="5"/>
+    <tableColumn id="26" name="Function-level5" dataDxfId="4"/>
+    <tableColumn id="27" name="Plausible6" dataDxfId="3"/>
+    <tableColumn id="28" name="Correct6" dataDxfId="2"/>
+    <tableColumn id="29" name="File-level6" dataDxfId="1"/>
+    <tableColumn id="30" name="Function-level6" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -9567,25 +9567,25 @@
       </c>
       <c r="AF8" s="3"/>
     </row>
-    <row r="9" spans="1:32" ht="144" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:32" ht="86.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="22">
         <v>7</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>149</v>
+      <c r="B9" s="34" t="s">
+        <v>262</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>150</v>
+        <v>263</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="23" t="s">
-        <v>7</v>
+        <v>264</v>
       </c>
       <c r="H9" s="6">
         <v>0</v>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="AF9" s="3"/>
     </row>
-    <row r="10" spans="1:32" ht="86.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:32" ht="115.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="22">
         <v>8</v>
       </c>
@@ -9670,17 +9670,17 @@
         <v>262</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="F10" s="22"/>
-      <c r="G10" s="22" t="s">
-        <v>272</v>
+      <c r="G10" s="23" t="s">
+        <v>268</v>
       </c>
       <c r="H10" s="6">
         <v>0</v>
@@ -14067,20 +14067,21 @@
     <hyperlink ref="G19" r:id="rId37"/>
     <hyperlink ref="G20" r:id="rId38"/>
     <hyperlink ref="G22" r:id="rId39"/>
-    <hyperlink ref="G9" r:id="rId40"/>
-    <hyperlink ref="G11" r:id="rId41"/>
-    <hyperlink ref="G12" r:id="rId42"/>
-    <hyperlink ref="G13" r:id="rId43"/>
-    <hyperlink ref="G14" r:id="rId44"/>
-    <hyperlink ref="G15" r:id="rId45"/>
-    <hyperlink ref="G16" r:id="rId46"/>
-    <hyperlink ref="G17" r:id="rId47"/>
-    <hyperlink ref="G18" r:id="rId48"/>
-    <hyperlink ref="G50" r:id="rId49"/>
+    <hyperlink ref="G11" r:id="rId40"/>
+    <hyperlink ref="G12" r:id="rId41"/>
+    <hyperlink ref="G13" r:id="rId42"/>
+    <hyperlink ref="G14" r:id="rId43"/>
+    <hyperlink ref="G15" r:id="rId44"/>
+    <hyperlink ref="G16" r:id="rId45"/>
+    <hyperlink ref="G17" r:id="rId46"/>
+    <hyperlink ref="G18" r:id="rId47"/>
+    <hyperlink ref="G50" r:id="rId48"/>
+    <hyperlink ref="G10" r:id="rId49"/>
+    <hyperlink ref="G9" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId50"/>
+    <tablePart r:id="rId51"/>
   </tableParts>
 </worksheet>
 </file>
@@ -36618,6 +36619,24 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="P123:T123"/>
+    <mergeCell ref="V123:Y123"/>
+    <mergeCell ref="P184:T184"/>
+    <mergeCell ref="V184:Y184"/>
+    <mergeCell ref="S231:W231"/>
+    <mergeCell ref="Y231:AB231"/>
+    <mergeCell ref="AR114:AV114"/>
+    <mergeCell ref="S111:W111"/>
+    <mergeCell ref="X111:AB111"/>
+    <mergeCell ref="AC111:AG111"/>
+    <mergeCell ref="AH111:AL111"/>
+    <mergeCell ref="AM111:AQ111"/>
+    <mergeCell ref="AR111:AV111"/>
+    <mergeCell ref="S114:W114"/>
+    <mergeCell ref="X114:AB114"/>
+    <mergeCell ref="AC114:AG114"/>
+    <mergeCell ref="AH114:AL114"/>
+    <mergeCell ref="AM114:AQ114"/>
     <mergeCell ref="AR84:AV84"/>
     <mergeCell ref="S47:W47"/>
     <mergeCell ref="X47:AB47"/>
@@ -36630,24 +36649,6 @@
     <mergeCell ref="AC84:AG84"/>
     <mergeCell ref="AH84:AL84"/>
     <mergeCell ref="AM84:AQ84"/>
-    <mergeCell ref="AR114:AV114"/>
-    <mergeCell ref="S111:W111"/>
-    <mergeCell ref="X111:AB111"/>
-    <mergeCell ref="AC111:AG111"/>
-    <mergeCell ref="AH111:AL111"/>
-    <mergeCell ref="AM111:AQ111"/>
-    <mergeCell ref="AR111:AV111"/>
-    <mergeCell ref="S114:W114"/>
-    <mergeCell ref="X114:AB114"/>
-    <mergeCell ref="AC114:AG114"/>
-    <mergeCell ref="AH114:AL114"/>
-    <mergeCell ref="AM114:AQ114"/>
-    <mergeCell ref="P123:T123"/>
-    <mergeCell ref="V123:Y123"/>
-    <mergeCell ref="P184:T184"/>
-    <mergeCell ref="V184:Y184"/>
-    <mergeCell ref="S231:W231"/>
-    <mergeCell ref="Y231:AB231"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="K2" r:id="rId1"/>
